--- a/samples/ss_bksi_cbng_ingest.xlsx
+++ b/samples/ss_bksi_cbng_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,65 +536,70 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -633,24 +638,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -685,24 +691,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -738,41 +745,46 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>BKASI7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>BKASI</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,3)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -808,41 +820,46 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>CIBNG7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>1 IBT (unit 3)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -875,30 +892,31 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -931,30 +949,31 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -989,24 +1008,25 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1039,34 +1059,35 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1101,24 +1122,25 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1153,24 +1175,25 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1205,24 +1228,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1257,24 +1281,25 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1307,34 +1332,35 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1367,34 +1393,35 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>single phi</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1429,24 +1456,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1479,38 +1507,39 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): SUKATANI Trf 1,2 / STRDA, KSBRU, DAWUAN</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1543,34 +1572,35 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>UP2B 2 (JABAR): NEW TAMBUN</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>SOURCE_BOUNDARY</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/ss_bksi_cbng_ingest.xlsx
+++ b/samples/ss_bksi_cbng_ingest.xlsx
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/samples/ss_bksi_cbng_ingest.xlsx
+++ b/samples/ss_bksi_cbng_ingest.xlsx
@@ -2438,7 +2438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2464,25 +2464,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -2507,21 +2512,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2542,21 +2548,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2577,21 +2584,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2612,21 +2620,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2647,21 +2656,22 @@
           <t>BKASI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2682,21 +2692,22 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2717,21 +2728,22 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2752,21 +2764,22 @@
           <t>CIBNG</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2865,12 +2878,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-1-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] Konfigurasi tidak ideal Single Phi di GIS Miniatur, GIS Pondok Kelapa dan GI Jatirangon, menyebabkan pembebanan tidak seimbang dan flow lebih besar pada SUTT 150 kV Pondok Kelapa-Jatirangon karena sudah berbeban diatas 60% apabila IBT Cibinong #3 off sehingga tidak memenuhi kriteria N- 1-1</t>
+          <t>[N-1-1] Konfigurasi tidak ideal Single Phi di GIS Miniatur, GIS Pondok Kelapa dan GI Jatirangon, menyebabkan pembebanan tidak seimbang dan flow lebih besar pada SUTT 150 kV Pondok Kelapa-Jatirangon karena sudah berbeban diatas 60% apabila IBT Cibinong #3 off sehingga tidak memenuhi kriteria N- 1-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2900,12 +2913,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] Fleksibilitas operasi Sub Sistem Bekasi 1,3-Cibinong 3 berkurang karena SUTT Bekasi - New Sukatani kondisi tidak siap operasi</t>
+          <t>[BELUM_DITETAPKAN] Fleksibilitas operasi Sub Sistem Bekasi 1,3-Cibinong 3 berkurang karena SUTT Bekasi - New Sukatani kondisi tidak siap operasi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/samples/ss_bksi_cbng_ingest.xlsx
+++ b/samples/ss_bksi_cbng_ingest.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,7 +717,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 1,3 Bekasi 500/150 kV</t>
+          <t>IBT 1 Bekasi 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -754,14 +754,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,3)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -792,12 +788,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 3 Cibinong 500/150 kV</t>
+          <t>IBT 3 Bekasi 500/150 kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 3 CIBNG7</t>
+          <t>IBT 3 BKASI7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -820,23 +816,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CIBNG7</t>
+          <t>BKASI7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>BKASI</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>1 IBT (unit 3)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -867,35 +859,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bekasi (bus 150 kV)</t>
+          <t>IBT 3 Cibinong 500/150 kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BKASI</t>
+          <t>IBT 3 CIBNG7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CIBNG7</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CIBNG</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>bus section + kopel</t>
+          <t>1 IBT (unit 3)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -907,10 +913,14 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -924,12 +934,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cibinong (bus 150 kV)</t>
+          <t>Bekasi (bus 150 kV)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CIBNG</t>
+          <t>BKASI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -981,12 +991,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sumur Recon</t>
+          <t>Cibinong (bus 150 kV)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SMRCN</t>
+          <t>CIBNG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -995,7 +1005,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1007,7 +1017,11 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
@@ -1034,17 +1048,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pondok Kelapa (GIS)</t>
+          <t>Sumur Recon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PDKLP</t>
+          <t>SMRCN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1060,11 +1074,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>single phi</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1074,14 +1084,10 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1095,17 +1101,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cibubur</t>
+          <t>Pondok Kelapa (GIS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CBBUR</t>
+          <t>PDKLP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1121,7 +1127,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>single phi</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1131,10 +1141,14 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1148,12 +1162,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gandaria</t>
+          <t>Cibubur</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GDRIA</t>
+          <t>CBBUR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1201,12 +1215,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Halim</t>
+          <t>Gandaria</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HALIM</t>
+          <t>GDRIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1215,7 +1229,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1254,12 +1268,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jatiwaringin</t>
+          <t>Halim</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JTWRG</t>
+          <t>HALIM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1307,17 +1321,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Miniatur (GIS)</t>
+          <t>Jatiwaringin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MNTUR</t>
+          <t>JTWRG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1333,11 +1347,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>single phi</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
@@ -1347,14 +1357,10 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1368,17 +1374,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jatirangon</t>
+          <t>Miniatur (GIS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JTRGN</t>
+          <t>MNTUR</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1429,12 +1435,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cireca/Cirencas</t>
+          <t>Jatirangon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CRCAS</t>
+          <t>JTRGN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1455,7 +1461,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>single phi</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
@@ -1465,10 +1475,14 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1482,12 +1496,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sukatani (UP2B Jabar)</t>
+          <t>Cireca/Cirencas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>CRCAS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1496,7 +1510,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1508,32 +1522,20 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>UP2B 2 (JABAR): SUKATANI Trf 1,2 / STRDA, KSBRU, DAWUAN</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1547,12 +1549,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New Tambun (UP2B Jabar)</t>
+          <t>Sukatani (UP2B Jabar)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NTMBN</t>
+          <t>SKTNI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1561,7 +1563,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1575,7 +1577,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>UP2B 2 (JABAR): NEW TAMBUN</t>
+          <t>UP2B 2 (JABAR): SUKATANI Trf 1,2 / STRDA, KSBRU, DAWUAN</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -1591,16 +1593,81 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>New Tambun (UP2B Jabar)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NTMBN</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UP2B 2 (JABAR): NEW TAMBUN</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
